--- a/TASK2/Scenariji/SC07_KreiranjeGrupnogTreninga.xlsx
+++ b/TASK2/Scenariji/SC07_KreiranjeGrupnogTreninga.xlsx
@@ -504,7 +504,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - uspjesan zavrsetak</t>
+          <t>Posljedice - uspješan završetak</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -516,7 +516,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - neuspjesan zavrsetak</t>
+          <t>Posljedice - neuspješan završetak</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -573,6 +573,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -662,6 +663,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -709,6 +711,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
